--- a/reports/cme9yo328000h9qwgg1fm0gid/2025/08/report___________________________08_2025.xlsx
+++ b/reports/cme9yo328000h9qwgg1fm0gid/2025/08/report___________________________08_2025.xlsx
@@ -85,7 +85,7 @@
     <t>Напомена:</t>
   </si>
   <si>
-    <t>Наплаћен износ у prepaid саобраћају у августу периоду</t>
+    <t>Наплаћен износ у undefined саобраћају у августу периоду</t>
   </si>
   <si>
     <t>01.08.2025 do 31.08.2025</t>
@@ -839,7 +839,7 @@
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>9</v>

--- a/reports/cme9yo328000h9qwgg1fm0gid/2025/08/report___________________________08_2025.xlsx
+++ b/reports/cme9yo328000h9qwgg1fm0gid/2025/08/report___________________________08_2025.xlsx
@@ -839,7 +839,7 @@
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>9</v>
